--- a/artfynd/A 30933-2026 artfynd.xlsx
+++ b/artfynd/A 30933-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,32 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134664987</v>
+        <v>135397117</v>
       </c>
       <c r="B5" t="n">
-        <v>99217</v>
+        <v>80488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795782</v>
+        <v>795982</v>
       </c>
       <c r="R5" t="n">
-        <v>7417046</v>
+        <v>7417253</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,27 +1092,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1122,131 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Rasmus Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rasmus Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134664987</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>795782</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7417046</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30933-2026 artfynd.xlsx
+++ b/artfynd/A 30933-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134664986</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665010</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135397117</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,8 +1272,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134664987</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30933-2026 artfynd.xlsx
+++ b/artfynd/A 30933-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>135397117</v>
       </c>
       <c r="B5" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30933-2026 artfynd.xlsx
+++ b/artfynd/A 30933-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>135397117</v>
       </c>
       <c r="B5" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30933-2026 artfynd.xlsx
+++ b/artfynd/A 30933-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,32 +1043,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134664987</v>
+        <v>135397117</v>
       </c>
       <c r="B5" t="n">
-        <v>99217</v>
+        <v>80556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795782</v>
+        <v>795982</v>
       </c>
       <c r="R5" t="n">
-        <v>7417046</v>
+        <v>7417253</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,27 +1112,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,16 +1142,137 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Rasmus Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Rasmus Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135397117</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134664987</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>795782</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7417046</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134664987</t>
         </is>
@@ -1168,6 +1284,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30933-2026 artfynd.xlsx
+++ b/artfynd/A 30933-2026 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>135397117</v>
       </c>
       <c r="B5" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
